--- a/public/Invistimo.xlsx
+++ b/public/Invistimo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benje\Documents\Projects\invite-system\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benje\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546EFCA-B6BB-4FB1-A80E-0D05E3E1185C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C4CFE9-BEAC-47AD-830F-20D2D7A5DA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,16 +52,16 @@
     <t>0527654321</t>
   </si>
   <si>
-    <t>משפחה</t>
-  </si>
-  <si>
-    <t>חברים</t>
-  </si>
-  <si>
     <t>כשר</t>
   </si>
   <si>
     <t>בהמתנה</t>
+  </si>
+  <si>
+    <t>משפחה קרובה</t>
+  </si>
+  <si>
+    <t>חברים רחוקים</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -468,16 +468,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -488,10 +488,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
       </c>
       <c r="E3">
         <v>1</v>

--- a/public/Invistimo.xlsx
+++ b/public/Invistimo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benje\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benje\Documents\Projects\invite-system\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C4CFE9-BEAC-47AD-830F-20D2D7A5DA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2477E014-1F01-4A0B-830D-7706D903BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
-  <si>
-    <t>שם</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>טלפון</t>
   </si>
@@ -55,13 +52,13 @@
     <t>כשר</t>
   </si>
   <si>
-    <t>בהמתנה</t>
-  </si>
-  <si>
     <t>משפחה קרובה</t>
   </si>
   <si>
     <t>חברים רחוקים</t>
+  </si>
+  <si>
+    <t>שם מלא</t>
   </si>
 </sst>
 </file>
@@ -442,55 +439,49 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3">
